--- a/skills/cpc-review/outputs/CPC_Master_Procurement_Register.xlsx
+++ b/skills/cpc-review/outputs/CPC_Master_Procurement_Register.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R874e9f4db6884786"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Procurement Reviews" sheetId="2" r:id="R5eff5cdf358b4bd9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Item Quotes" sheetId="3" r:id="R62e010df50044307"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Awards" sheetId="4" r:id="Rcafc6ebc9242456c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Master Item History" sheetId="5" r:id="R19025fda6ccb489a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Item Catalog" sheetId="6" r:id="Ra759c3ed414c43f4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vendors" sheetId="7" r:id="Rfa218bc31fc04048"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Item Aliases" sheetId="8" r:id="Re86b391fe8354d81"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R19e10c9592b54cbc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Procurement Reviews" sheetId="2" r:id="R5d8b4df84c5541ab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Item Quotes" sheetId="3" r:id="Re316127e8ab643e1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Awards" sheetId="4" r:id="R0023cbdf333d4508"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Master Item History" sheetId="5" r:id="R6139ea3c3a584043"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Item Catalog" sheetId="6" r:id="R355589ad85ba4f06"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vendors" sheetId="7" r:id="R6778b414046a41b2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Item Aliases" sheetId="8" r:id="Rd7497aafc992490f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -73,7 +73,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="28">
+  <x:cellXfs count="26">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -102,14 +102,8 @@
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" wrapText="1"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
@@ -332,11 +326,14 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="4" max="4" width="24" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="24" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="24" hidden="0" customWidth="1"/>
     <x:col min="1" max="1" width="20.5" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="4.75" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
@@ -358,31 +355,13 @@
       <x:c r="B3" s="12" t="str">
         <x:v>Value</x:v>
       </x:c>
-      <x:c r="D3" s="16" t="str">
-        <x:v>Historical comparison</x:v>
-      </x:c>
-      <x:c r="E3" s="16" t="str">
-        <x:v>Meaning</x:v>
-      </x:c>
-      <x:c r="F3" s="16" t="str">
-        <x:v>CPC use</x:v>
-      </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" t="str">
         <x:v>CPC reviews</x:v>
       </x:c>
       <x:c r="B4" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D4" s="17" t="str">
-        <x:v>WITHIN_HISTORY_BAND</x:v>
-      </x:c>
-      <x:c r="E4" s="17" t="str">
-        <x:v>&lt;10% variance</x:v>
-      </x:c>
-      <x:c r="F4" s="17" t="str">
-        <x:v>Normal review</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -390,16 +369,7 @@
         <x:v>Vendor quote rows</x:v>
       </x:c>
       <x:c r="B5" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D5" s="17" t="str">
-        <x:v>REVIEW</x:v>
-      </x:c>
-      <x:c r="E5" s="17" t="str">
-        <x:v>&gt;=10%</x:v>
-      </x:c>
-      <x:c r="F5" s="17" t="str">
-        <x:v>Check reasons</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -409,15 +379,6 @@
       <x:c r="B6" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D6" s="17" t="str">
-        <x:v>HIGH_REVIEW</x:v>
-      </x:c>
-      <x:c r="E6" s="17" t="str">
-        <x:v>&gt;=20%</x:v>
-      </x:c>
-      <x:c r="F6" s="17" t="str">
-        <x:v>Seek stronger validation</x:v>
-      </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" t="str">
@@ -426,57 +387,48 @@
       <x:c r="B7" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D7" s="17" t="str">
-        <x:v>CRITICAL_REVIEW</x:v>
-      </x:c>
-      <x:c r="E7" s="17" t="str">
-        <x:v>&gt;=30%</x:v>
-      </x:c>
-      <x:c r="F7" s="17" t="str">
-        <x:v>Validate thoroughly; not an automatic rejection</x:v>
-      </x:c>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="17" t="str">
+      <x:c r="A9" s="16" t="str">
         <x:v>CSV files are the source of truth. This workbook is generated for analysis. Historical rates are benchmark signals only; CPC must confirm specification, unit, quantity, freight, installation, tax, geography and timing before judging price.</x:v>
       </x:c>
-      <x:c r="B9" s="17"/>
-      <x:c r="C9" s="17"/>
-      <x:c r="D9" s="17"/>
-      <x:c r="E9" s="17"/>
-      <x:c r="F9" s="17"/>
-      <x:c r="G9" s="17"/>
-      <x:c r="H9" s="17"/>
+      <x:c r="B9" s="16"/>
+      <x:c r="C9" s="16"/>
+      <x:c r="D9" s="16"/>
+      <x:c r="E9" s="16"/>
+      <x:c r="F9" s="16"/>
+      <x:c r="G9" s="16"/>
+      <x:c r="H9" s="16"/>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="17"/>
-      <x:c r="B10" s="17"/>
-      <x:c r="C10" s="17"/>
-      <x:c r="D10" s="17"/>
-      <x:c r="E10" s="17"/>
-      <x:c r="F10" s="17"/>
-      <x:c r="G10" s="17"/>
-      <x:c r="H10" s="17"/>
+      <x:c r="A10" s="16"/>
+      <x:c r="B10" s="16"/>
+      <x:c r="C10" s="16"/>
+      <x:c r="D10" s="16"/>
+      <x:c r="E10" s="16"/>
+      <x:c r="F10" s="16"/>
+      <x:c r="G10" s="16"/>
+      <x:c r="H10" s="16"/>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="17"/>
-      <x:c r="B11" s="17"/>
-      <x:c r="C11" s="17"/>
-      <x:c r="D11" s="17"/>
-      <x:c r="E11" s="17"/>
-      <x:c r="F11" s="17"/>
-      <x:c r="G11" s="17"/>
-      <x:c r="H11" s="17"/>
+      <x:c r="A11" s="16"/>
+      <x:c r="B11" s="16"/>
+      <x:c r="C11" s="16"/>
+      <x:c r="D11" s="16"/>
+      <x:c r="E11" s="16"/>
+      <x:c r="F11" s="16"/>
+      <x:c r="G11" s="16"/>
+      <x:c r="H11" s="16"/>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="17"/>
-      <x:c r="B12" s="17"/>
-      <x:c r="C12" s="17"/>
-      <x:c r="D12" s="17"/>
-      <x:c r="E12" s="17"/>
-      <x:c r="F12" s="17"/>
-      <x:c r="G12" s="17"/>
-      <x:c r="H12" s="17"/>
+      <x:c r="A12" s="16"/>
+      <x:c r="B12" s="16"/>
+      <x:c r="C12" s="16"/>
+      <x:c r="D12" s="16"/>
+      <x:c r="E12" s="16"/>
+      <x:c r="F12" s="16"/>
+      <x:c r="G12" s="16"/>
+      <x:c r="H12" s="16"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -491,121 +443,285 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="12.880000114440918" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="34.75" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="10" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="14.75" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="11.25" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="6.25" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="4.25" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="9.880000114440918" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="5.880000114440918" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="11.130000114440918" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="13" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="22" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="8.380000114440918" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="30.3799991607666" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="13" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="17.8799991607666" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18.6299991607666" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="19.8799991607666" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="61.630001068115234" hidden="0" customWidth="1"/>
     <x:col min="13" max="13" width="19" hidden="0" customWidth="1"/>
     <x:col min="14" max="14" width="7.130000114440918" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="14" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="49.130001068115234" hidden="0" customWidth="1"/>
     <x:col min="16" max="16" width="14.630000114440918" hidden="0" customWidth="1"/>
-    <x:col min="17" max="17" width="9.25" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="9.630000114440918" hidden="0" customWidth="1"/>
     <x:col min="18" max="18" width="9.380000114440918" hidden="0" customWidth="1"/>
     <x:col min="19" max="19" width="22.5" hidden="0" customWidth="1"/>
-    <x:col min="20" max="20" width="13.75" hidden="0" customWidth="1"/>
-    <x:col min="21" max="21" width="10" hidden="0" customWidth="1"/>
+    <x:col min="20" max="20" width="255" hidden="0" customWidth="1"/>
+    <x:col min="21" max="21" width="57.880001068115234" hidden="0" customWidth="1"/>
     <x:col min="22" max="22" width="10.5" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="23" t="str">
+      <x:c r="A1" s="21" t="str">
         <x:v>procurement_id</x:v>
       </x:c>
-      <x:c r="B1" s="23" t="str">
+      <x:c r="B1" s="21" t="str">
         <x:v>review_date</x:v>
       </x:c>
-      <x:c r="C1" s="23" t="str">
+      <x:c r="C1" s="21" t="str">
         <x:v>procurement_date</x:v>
       </x:c>
-      <x:c r="D1" s="23" t="str">
+      <x:c r="D1" s="21" t="str">
         <x:v>financial_year</x:v>
       </x:c>
-      <x:c r="E1" s="23" t="str">
+      <x:c r="E1" s="21" t="str">
         <x:v>quarter</x:v>
       </x:c>
-      <x:c r="F1" s="23" t="str">
+      <x:c r="F1" s="21" t="str">
         <x:v>state</x:v>
       </x:c>
-      <x:c r="G1" s="23" t="str">
+      <x:c r="G1" s="21" t="str">
         <x:v>project_unit</x:v>
       </x:c>
-      <x:c r="H1" s="23" t="str">
+      <x:c r="H1" s="21" t="str">
         <x:v>district</x:v>
       </x:c>
-      <x:c r="I1" s="23" t="str">
+      <x:c r="I1" s="21" t="str">
         <x:v>project_name</x:v>
       </x:c>
-      <x:c r="J1" s="23" t="str">
+      <x:c r="J1" s="21" t="str">
         <x:v>funding_partner</x:v>
       </x:c>
-      <x:c r="K1" s="23" t="str">
+      <x:c r="K1" s="21" t="str">
         <x:v>procurement_category</x:v>
       </x:c>
-      <x:c r="L1" s="23" t="str">
+      <x:c r="L1" s="21" t="str">
         <x:v>procurement_reference</x:v>
       </x:c>
-      <x:c r="M1" s="23" t="str">
+      <x:c r="M1" s="21" t="str">
         <x:v>approved_budget_value</x:v>
       </x:c>
-      <x:c r="N1" s="23" t="str">
+      <x:c r="N1" s="21" t="str">
         <x:v>currency</x:v>
       </x:c>
-      <x:c r="O1" s="23" t="str">
+      <x:c r="O1" s="21" t="str">
         <x:v>proposed_vendor</x:v>
       </x:c>
-      <x:c r="P1" s="23" t="str">
+      <x:c r="P1" s="21" t="str">
         <x:v>proposed_amount</x:v>
       </x:c>
-      <x:c r="Q1" s="23" t="str">
+      <x:c r="Q1" s="21" t="str">
         <x:v>cpc_verdict</x:v>
       </x:c>
-      <x:c r="R1" s="23" t="str">
+      <x:c r="R1" s="21" t="str">
         <x:v>final_status</x:v>
       </x:c>
-      <x:c r="S1" s="23" t="str">
+      <x:c r="S1" s="21" t="str">
         <x:v>price_reasonableness_status</x:v>
       </x:c>
-      <x:c r="T1" s="23" t="str">
+      <x:c r="T1" s="21" t="str">
         <x:v>source_reference</x:v>
       </x:c>
-      <x:c r="U1" s="23" t="str">
+      <x:c r="U1" s="21" t="str">
         <x:v>record_hash</x:v>
       </x:c>
-      <x:c r="V1" s="23" t="str">
+      <x:c r="V1" s="21" t="str">
         <x:v>last_updated</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="17"/>
-      <x:c r="B2" s="17"/>
-      <x:c r="C2" s="17"/>
-      <x:c r="D2" s="17"/>
-      <x:c r="E2" s="17"/>
-      <x:c r="F2" s="17"/>
-      <x:c r="G2" s="17"/>
-      <x:c r="H2" s="17"/>
-      <x:c r="I2" s="17"/>
-      <x:c r="J2" s="17"/>
-      <x:c r="K2" s="17"/>
-      <x:c r="L2" s="17"/>
-      <x:c r="M2" s="17"/>
-      <x:c r="N2" s="17"/>
-      <x:c r="O2" s="17"/>
-      <x:c r="P2" s="17"/>
-      <x:c r="Q2" s="17"/>
-      <x:c r="R2" s="17"/>
-      <x:c r="S2" s="17"/>
-      <x:c r="T2" s="17"/>
-      <x:c r="U2" s="17"/>
-      <x:c r="V2" s="17"/>
+      <x:c r="A2" s="16" t="str">
+        <x:v>PROC-HIST-GJ-VIS-2026-01-BAG-BOTTLE</x:v>
+      </x:c>
+      <x:c r="B2" s="16" t="str">
+        <x:v>2026-02-11</x:v>
+      </x:c>
+      <x:c r="C2" s="16" t="str">
+        <x:v>2026-01-29</x:v>
+      </x:c>
+      <x:c r="D2" s="16" t="str">
+        <x:v>2025-26</x:v>
+      </x:c>
+      <x:c r="E2" s="16" t="str">
+        <x:v>Q4</x:v>
+      </x:c>
+      <x:c r="F2" s="16" t="str">
+        <x:v>Gujarat</x:v>
+      </x:c>
+      <x:c r="G2" s="16" t="str">
+        <x:v>Visnagar / North Gujarat PUs</x:v>
+      </x:c>
+      <x:c r="H2" s="16" t="str">
+        <x:v>Mahesana</x:v>
+      </x:c>
+      <x:c r="I2" s="16" t="str">
+        <x:v>BCI Programme - Staff Welfare / Staff Kit</x:v>
+      </x:c>
+      <x:c r="J2" s="16" t="str">
+        <x:v>BCI</x:v>
+      </x:c>
+      <x:c r="K2" s="16" t="str">
+        <x:v>Staff kit / office supplies</x:v>
+      </x:c>
+      <x:c r="L2" s="16" t="str">
+        <x:v>Office bag and bottle purchase - purchase note/comparative summary 29-01-2026</x:v>
+      </x:c>
+      <x:c r="M2" s="16" t="str"/>
+      <x:c r="N2" s="16" t="str">
+        <x:v>INR</x:v>
+      </x:c>
+      <x:c r="O2" s="16" t="str">
+        <x:v>Item-wise L1: Mehul Vasan Bhandar (bottle); ASE Enterprise (bag)</x:v>
+      </x:c>
+      <x:c r="P2" s="16" t="str"/>
+      <x:c r="Q2" s="16" t="str">
+        <x:v>AMBER</x:v>
+      </x:c>
+      <x:c r="R2" s="16" t="str">
+        <x:v>pending</x:v>
+      </x:c>
+      <x:c r="S2" s="16" t="str">
+        <x:v>partially established</x:v>
+      </x:c>
+      <x:c r="T2" s="16" t="str">
+        <x:v>Gmail - Fwd_ office bag and bottle purchase(2).pdf; CPC response 11-02-2026 and follow-up 24-02-2026. Historical AMBER mapping reflects bottle allowed to proceed while bag required quality/rate justification. No final PO/payment evidence recovered.</x:v>
+      </x:c>
+      <x:c r="U2" s="16" t="str">
+        <x:v>29bbf411cf31e28cb51478f565de1d1dc181c9f2df0fc05a72002fd4306f70ee</x:v>
+      </x:c>
+      <x:c r="V2" s="16" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="16" t="str">
+        <x:v>PROC-HIST-MP-LKD-2026-08-LAPTOP</x:v>
+      </x:c>
+      <x:c r="B3" s="16" t="str">
+        <x:v>2026-09-02</x:v>
+      </x:c>
+      <x:c r="C3" s="16" t="str">
+        <x:v>2026-08-24</x:v>
+      </x:c>
+      <x:c r="D3" s="16" t="str">
+        <x:v>2026-27</x:v>
+      </x:c>
+      <x:c r="E3" s="16" t="str">
+        <x:v>Q2</x:v>
+      </x:c>
+      <x:c r="F3" s="16" t="str">
+        <x:v>Madhya Pradesh</x:v>
+      </x:c>
+      <x:c r="G3" s="16" t="str">
+        <x:v>Lakhnadon &amp; Ghansur, Seoni</x:v>
+      </x:c>
+      <x:c r="H3" s="16" t="str">
+        <x:v>Seoni</x:v>
+      </x:c>
+      <x:c r="I3" s="16" t="str">
+        <x:v>Focus Development Project-HDFC</x:v>
+      </x:c>
+      <x:c r="J3" s="16" t="str">
+        <x:v>HDFC</x:v>
+      </x:c>
+      <x:c r="K3" s="16" t="str">
+        <x:v>IT equipment</x:v>
+      </x:c>
+      <x:c r="L3" s="16" t="str">
+        <x:v>DSC/LKD/04/2026</x:v>
+      </x:c>
+      <x:c r="M3" s="16" t="str"/>
+      <x:c r="N3" s="16" t="str">
+        <x:v>INR</x:v>
+      </x:c>
+      <x:c r="O3" s="16" t="str">
+        <x:v>Computer Vision, Jabalpur</x:v>
+      </x:c>
+      <x:c r="P3" s="16" t="str">
+        <x:v>226500</x:v>
+      </x:c>
+      <x:c r="Q3" s="16" t="str">
+        <x:v>UNVERIFIED</x:v>
+      </x:c>
+      <x:c r="R3" s="16" t="str">
+        <x:v>pending</x:v>
+      </x:c>
+      <x:c r="S3" s="16" t="str">
+        <x:v>not established</x:v>
+      </x:c>
+      <x:c r="T3" s="16" t="str">
+        <x:v>Purchase Committee Note _Laptop.docx.pdf and Gmail - Fwd_ Regarding Procurement of the Laptop under FDP, Lakhnadon, Seoni.pdf. Purchase committee recommended Computer Vision at ₹226,000 plus ₹500 local transport; one recommendation line incorrectly names Sethi Batteries. No final CPC approval/PO/payment evidence recovered.</x:v>
+      </x:c>
+      <x:c r="U3" s="16" t="str">
+        <x:v>c6ca29be7c657b8ec9b0e39f1d21177e8f5e42b220681173fada15ae43c24f18</x:v>
+      </x:c>
+      <x:c r="V3" s="16" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="16" t="str">
+        <x:v>PROC-HIST-MH-NAR-2026-09-GRASS-SEEDING</x:v>
+      </x:c>
+      <x:c r="B4" s="16" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+      <x:c r="C4" s="16" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+      <x:c r="D4" s="16" t="str">
+        <x:v>2026-27</x:v>
+      </x:c>
+      <x:c r="E4" s="16" t="str">
+        <x:v>Q2</x:v>
+      </x:c>
+      <x:c r="F4" s="16" t="str">
+        <x:v>Maharashtra</x:v>
+      </x:c>
+      <x:c r="G4" s="16" t="str">
+        <x:v>Narayangaon</x:v>
+      </x:c>
+      <x:c r="H4" s="16" t="str">
+        <x:v>Pune</x:v>
+      </x:c>
+      <x:c r="I4" s="16" t="str"/>
+      <x:c r="J4" s="16" t="str"/>
+      <x:c r="K4" s="16" t="str">
+        <x:v>Biodiversity / field activity</x:v>
+      </x:c>
+      <x:c r="L4" s="16" t="str">
+        <x:v>Comparative Note for Grass seeding (Biodiversity) - 10-09-2026</x:v>
+      </x:c>
+      <x:c r="M4" s="16" t="str"/>
+      <x:c r="N4" s="16" t="str">
+        <x:v>INR</x:v>
+      </x:c>
+      <x:c r="O4" s="16" t="str"/>
+      <x:c r="P4" s="16" t="str"/>
+      <x:c r="Q4" s="16" t="str">
+        <x:v>UNVERIFIED</x:v>
+      </x:c>
+      <x:c r="R4" s="16" t="str">
+        <x:v>pending</x:v>
+      </x:c>
+      <x:c r="S4" s="16" t="str">
+        <x:v>not assessed</x:v>
+      </x:c>
+      <x:c r="T4" s="16" t="str">
+        <x:v>Gmail - Comparative Note for Grass seeding (Biodiversity).pdf. Email confirms a field-unit purchase plan, comparative/acceptance, vendor checklist and quotation pack were submitted to CPC, but the attachment contents/rates/vendors are not recoverable from the saved email PDF. No CPC conclusion recovered.</x:v>
+      </x:c>
+      <x:c r="U4" s="16" t="str">
+        <x:v>bcd788d7bf80dca246e8675629c1e4e58b5a0a00930a20017f3bf0a1e2980f61</x:v>
+      </x:c>
+      <x:c r="V4" s="16" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -616,19 +732,19 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="7.380000114440918" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="12.880000114440918" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="6.380000114440918" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="17.8799991607666" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="30.25" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="16.5" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="20.1299991607666" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18.6299991607666" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="11.5" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="10.130000114440918" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="13.630000114440918" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="139.25" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="33.130001068115234" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="7" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="10" hidden="0" customWidth="1"/>
     <x:col min="11" max="11" width="11.75" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="8.25" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="11.130000114440918" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="16.8799991607666" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="21.75" hidden="0" customWidth="1"/>
     <x:col min="14" max="14" width="9.380000114440918" hidden="0" customWidth="1"/>
     <x:col min="15" max="15" width="12" hidden="0" customWidth="1"/>
     <x:col min="16" max="16" width="9.5" hidden="0" customWidth="1"/>
@@ -638,284 +754,459 @@
     <x:col min="20" max="20" width="14.5" hidden="0" customWidth="1"/>
     <x:col min="21" max="21" width="13.75" hidden="0" customWidth="1"/>
     <x:col min="22" max="22" width="12.5" hidden="0" customWidth="1"/>
-    <x:col min="23" max="23" width="12.130000114440918" hidden="0" customWidth="1"/>
+    <x:col min="23" max="23" width="43.5" hidden="0" customWidth="1"/>
     <x:col min="24" max="24" width="12.5" hidden="0" customWidth="1"/>
     <x:col min="25" max="25" width="13" hidden="0" customWidth="1"/>
     <x:col min="26" max="26" width="8.75" hidden="0" customWidth="1"/>
     <x:col min="27" max="27" width="22.8799991607666" hidden="0" customWidth="1"/>
-    <x:col min="28" max="28" width="14.25" hidden="0" customWidth="1"/>
+    <x:col min="28" max="28" width="112.37999725341797" hidden="0" customWidth="1"/>
     <x:col min="29" max="29" width="21.5" hidden="0" customWidth="1"/>
     <x:col min="30" max="30" width="10.5" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="23" t="str">
+      <x:c r="A1" s="21" t="str">
         <x:v>quote_id</x:v>
       </x:c>
-      <x:c r="B1" s="23" t="str">
+      <x:c r="B1" s="21" t="str">
         <x:v>procurement_id</x:v>
       </x:c>
-      <x:c r="C1" s="23" t="str">
+      <x:c r="C1" s="21" t="str">
         <x:v>item_id</x:v>
       </x:c>
-      <x:c r="D1" s="23" t="str">
+      <x:c r="D1" s="21" t="str">
         <x:v>original_item_description</x:v>
       </x:c>
-      <x:c r="E1" s="23" t="str">
+      <x:c r="E1" s="21" t="str">
         <x:v>normalized_item_name</x:v>
       </x:c>
-      <x:c r="F1" s="23" t="str">
+      <x:c r="F1" s="21" t="str">
         <x:v>item_category</x:v>
       </x:c>
-      <x:c r="G1" s="23" t="str">
+      <x:c r="G1" s="21" t="str">
         <x:v>specification</x:v>
       </x:c>
-      <x:c r="H1" s="23" t="str">
+      <x:c r="H1" s="21" t="str">
         <x:v>specification_key</x:v>
       </x:c>
-      <x:c r="I1" s="23" t="str">
+      <x:c r="I1" s="21" t="str">
         <x:v>quantity</x:v>
       </x:c>
-      <x:c r="J1" s="23" t="str">
+      <x:c r="J1" s="21" t="str">
         <x:v>quoted_unit</x:v>
       </x:c>
-      <x:c r="K1" s="23" t="str">
+      <x:c r="K1" s="21" t="str">
         <x:v>canonical_unit</x:v>
       </x:c>
-      <x:c r="L1" s="23" t="str">
+      <x:c r="L1" s="21" t="str">
         <x:v>vendor_id</x:v>
       </x:c>
-      <x:c r="M1" s="23" t="str">
+      <x:c r="M1" s="21" t="str">
         <x:v>vendor_name</x:v>
       </x:c>
-      <x:c r="N1" s="23" t="str">
+      <x:c r="N1" s="21" t="str">
         <x:v>quote_date</x:v>
       </x:c>
-      <x:c r="O1" s="23" t="str">
+      <x:c r="O1" s="21" t="str">
         <x:v>base_unit_rate</x:v>
       </x:c>
-      <x:c r="P1" s="23" t="str">
+      <x:c r="P1" s="21" t="str">
         <x:v>gst_percent</x:v>
       </x:c>
-      <x:c r="Q1" s="23" t="str">
+      <x:c r="Q1" s="21" t="str">
         <x:v>freight_per_unit</x:v>
       </x:c>
-      <x:c r="R1" s="23" t="str">
+      <x:c r="R1" s="21" t="str">
         <x:v>installation_per_unit</x:v>
       </x:c>
-      <x:c r="S1" s="23" t="str">
+      <x:c r="S1" s="21" t="str">
         <x:v>other_per_unit</x:v>
       </x:c>
-      <x:c r="T1" s="23" t="str">
+      <x:c r="T1" s="21" t="str">
         <x:v>discount_per_unit</x:v>
       </x:c>
-      <x:c r="U1" s="23" t="str">
+      <x:c r="U1" s="21" t="str">
         <x:v>landed_unit_rate</x:v>
       </x:c>
-      <x:c r="V1" s="23" t="str">
+      <x:c r="V1" s="21" t="str">
         <x:v>evaluated_total</x:v>
       </x:c>
-      <x:c r="W1" s="23" t="str">
+      <x:c r="W1" s="21" t="str">
         <x:v>responsiveness</x:v>
       </x:c>
-      <x:c r="X1" s="23" t="str">
+      <x:c r="X1" s="21" t="str">
         <x:v>numerical_rank</x:v>
       </x:c>
-      <x:c r="Y1" s="23" t="str">
+      <x:c r="Y1" s="21" t="str">
         <x:v>responsive_rank</x:v>
       </x:c>
-      <x:c r="Z1" s="23" t="str">
+      <x:c r="Z1" s="21" t="str">
         <x:v>negotiated</x:v>
       </x:c>
-      <x:c r="AA1" s="23" t="str">
+      <x:c r="AA1" s="21" t="str">
         <x:v>negotiated_landed_unit_rate</x:v>
       </x:c>
-      <x:c r="AB1" s="23" t="str">
+      <x:c r="AB1" s="21" t="str">
         <x:v>source_document</x:v>
       </x:c>
-      <x:c r="AC1" s="23" t="str">
+      <x:c r="AC1" s="21" t="str">
         <x:v>benchmark_reference_only</x:v>
       </x:c>
-      <x:c r="AD1" s="23" t="str">
+      <x:c r="AD1" s="21" t="str">
         <x:v>last_updated</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="17"/>
-      <x:c r="B2" s="17"/>
-      <x:c r="C2" s="17"/>
-      <x:c r="D2" s="17"/>
-      <x:c r="E2" s="17"/>
-      <x:c r="F2" s="17"/>
-      <x:c r="G2" s="17"/>
-      <x:c r="H2" s="17"/>
-      <x:c r="I2" s="17"/>
-      <x:c r="J2" s="17"/>
-      <x:c r="K2" s="17"/>
-      <x:c r="L2" s="17"/>
-      <x:c r="M2" s="17"/>
-      <x:c r="N2" s="17"/>
-      <x:c r="O2" s="17"/>
-      <x:c r="P2" s="17"/>
-      <x:c r="Q2" s="17"/>
-      <x:c r="R2" s="17"/>
-      <x:c r="S2" s="17"/>
-      <x:c r="T2" s="17"/>
-      <x:c r="U2" s="17"/>
-      <x:c r="V2" s="17"/>
-      <x:c r="W2" s="17"/>
-      <x:c r="X2" s="17"/>
-      <x:c r="Y2" s="17"/>
-      <x:c r="Z2" s="17"/>
-      <x:c r="AA2" s="17"/>
-      <x:c r="AB2" s="17"/>
-      <x:c r="AC2" s="17"/>
-      <x:c r="AD2" s="17"/>
-    </x:row>
-  </x:sheetData>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</x:worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="7.630000114440918" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="12.880000114440918" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="6.380000114440918" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="18.6299991607666" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="11.5" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="10.130000114440918" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="13.630000114440918" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="11.75" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="14.5" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="8.25" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="11.130000114440918" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="9.630000114440918" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="19.6299991607666" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="9.5" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="13" hidden="0" customWidth="1"/>
-    <x:col min="16" max="16" width="16.5" hidden="0" customWidth="1"/>
-    <x:col min="17" max="17" width="12.130000114440918" hidden="0" customWidth="1"/>
-    <x:col min="18" max="18" width="21.25" hidden="0" customWidth="1"/>
-    <x:col min="19" max="19" width="9.75" hidden="0" customWidth="1"/>
-    <x:col min="20" max="20" width="7.130000114440918" hidden="0" customWidth="1"/>
-    <x:col min="21" max="21" width="9.25" hidden="0" customWidth="1"/>
-    <x:col min="22" max="22" width="9.380000114440918" hidden="0" customWidth="1"/>
-    <x:col min="23" max="23" width="15.5" hidden="0" customWidth="1"/>
-    <x:col min="24" max="24" width="23.1299991607666" hidden="0" customWidth="1"/>
-    <x:col min="25" max="25" width="13.75" hidden="0" customWidth="1"/>
-    <x:col min="26" max="26" width="10.5" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" s="23" t="str">
-        <x:v>award_id</x:v>
-      </x:c>
-      <x:c r="B1" s="23" t="str">
-        <x:v>procurement_id</x:v>
-      </x:c>
-      <x:c r="C1" s="23" t="str">
-        <x:v>item_id</x:v>
-      </x:c>
-      <x:c r="D1" s="23" t="str">
-        <x:v>normalized_item_name</x:v>
-      </x:c>
-      <x:c r="E1" s="23" t="str">
-        <x:v>item_category</x:v>
-      </x:c>
-      <x:c r="F1" s="23" t="str">
-        <x:v>specification</x:v>
-      </x:c>
-      <x:c r="G1" s="23" t="str">
-        <x:v>specification_key</x:v>
-      </x:c>
-      <x:c r="H1" s="23" t="str">
-        <x:v>canonical_unit</x:v>
-      </x:c>
-      <x:c r="I1" s="23" t="str">
-        <x:v>awarded_quantity</x:v>
-      </x:c>
-      <x:c r="J1" s="23" t="str">
-        <x:v>vendor_id</x:v>
-      </x:c>
-      <x:c r="K1" s="23" t="str">
-        <x:v>vendor_name</x:v>
-      </x:c>
-      <x:c r="L1" s="23" t="str">
-        <x:v>award_date</x:v>
-      </x:c>
-      <x:c r="M1" s="23" t="str">
-        <x:v>awarded_base_unit_rate</x:v>
-      </x:c>
-      <x:c r="N1" s="23" t="str">
-        <x:v>gst_percent</x:v>
-      </x:c>
-      <x:c r="O1" s="23" t="str">
-        <x:v>freight_per_unit</x:v>
-      </x:c>
-      <x:c r="P1" s="23" t="str">
-        <x:v>installation_per_unit</x:v>
-      </x:c>
-      <x:c r="Q1" s="23" t="str">
-        <x:v>other_per_unit</x:v>
-      </x:c>
-      <x:c r="R1" s="23" t="str">
-        <x:v>awarded_landed_unit_rate</x:v>
-      </x:c>
-      <x:c r="S1" s="23" t="str">
-        <x:v>award_total</x:v>
-      </x:c>
-      <x:c r="T1" s="23" t="str">
-        <x:v>currency</x:v>
-      </x:c>
-      <x:c r="U1" s="23" t="str">
-        <x:v>cpc_verdict</x:v>
-      </x:c>
-      <x:c r="V1" s="23" t="str">
-        <x:v>final_status</x:v>
-      </x:c>
-      <x:c r="W1" s="23" t="str">
-        <x:v>benchmark_eligible</x:v>
-      </x:c>
-      <x:c r="X1" s="23" t="str">
-        <x:v>benchmark_exclusion_reason</x:v>
-      </x:c>
-      <x:c r="Y1" s="23" t="str">
-        <x:v>source_reference</x:v>
-      </x:c>
-      <x:c r="Z1" s="23" t="str">
-        <x:v>last_updated</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2">
-      <x:c r="A2" s="17"/>
-      <x:c r="B2" s="17"/>
-      <x:c r="C2" s="17"/>
-      <x:c r="D2" s="17"/>
-      <x:c r="E2" s="17"/>
-      <x:c r="F2" s="17"/>
-      <x:c r="G2" s="17"/>
-      <x:c r="H2" s="17"/>
-      <x:c r="I2" s="17"/>
-      <x:c r="J2" s="17"/>
-      <x:c r="K2" s="17"/>
-      <x:c r="L2" s="17"/>
-      <x:c r="M2" s="17"/>
-      <x:c r="N2" s="17"/>
-      <x:c r="O2" s="17"/>
-      <x:c r="P2" s="17"/>
-      <x:c r="Q2" s="17"/>
-      <x:c r="R2" s="17"/>
-      <x:c r="S2" s="17"/>
-      <x:c r="T2" s="17"/>
-      <x:c r="U2" s="17"/>
-      <x:c r="V2" s="17"/>
-      <x:c r="W2" s="17"/>
-      <x:c r="X2" s="17"/>
-      <x:c r="Y2" s="17"/>
-      <x:c r="Z2" s="17"/>
+      <x:c r="A2" s="16" t="str">
+        <x:v>QUOTE-AB29C647329C</x:v>
+      </x:c>
+      <x:c r="B2" s="16" t="str">
+        <x:v>PROC-HIST-GJ-VIS-2026-01-BAG-BOTTLE</x:v>
+      </x:c>
+      <x:c r="C2" s="16" t="str">
+        <x:v>ITEM-BDBB344470B0</x:v>
+      </x:c>
+      <x:c r="D2" s="16" t="str">
+        <x:v>Cold water bottle</x:v>
+      </x:c>
+      <x:c r="E2" s="16" t="str">
+        <x:v>office water bottle</x:v>
+      </x:c>
+      <x:c r="F2" s="16" t="str">
+        <x:v>Staff kit</x:v>
+      </x:c>
+      <x:c r="G2" s="16" t="str">
+        <x:v>Detailed bottle specification not recovered. CPC email records L1 vendor Mehul Vasan Bhandar at a rate of ₹750 for 70 quantity; GST was stated as included but GSTIN was initially missing.</x:v>
+      </x:c>
+      <x:c r="H2" s="16" t="str">
+        <x:v>UNSPECIFIED</x:v>
+      </x:c>
+      <x:c r="I2" s="16" t="str">
+        <x:v>70.0</x:v>
+      </x:c>
+      <x:c r="J2" s="16" t="str">
+        <x:v>unit</x:v>
+      </x:c>
+      <x:c r="K2" s="16" t="str">
+        <x:v>unit</x:v>
+      </x:c>
+      <x:c r="L2" s="16" t="str">
+        <x:v>VEND-59C44BBC65A6</x:v>
+      </x:c>
+      <x:c r="M2" s="16" t="str">
+        <x:v>Mehul Vasan Bhandar</x:v>
+      </x:c>
+      <x:c r="N2" s="16" t="str">
+        <x:v>2026-01-23</x:v>
+      </x:c>
+      <x:c r="O2" s="16" t="str">
+        <x:v>750</x:v>
+      </x:c>
+      <x:c r="P2" s="16" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q2" s="16" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R2" s="16" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S2" s="16" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T2" s="16" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U2" s="16" t="str">
+        <x:v>750.0</x:v>
+      </x:c>
+      <x:c r="V2" s="16" t="str">
+        <x:v>52500.0</x:v>
+      </x:c>
+      <x:c r="W2" s="16" t="str">
+        <x:v>Responsive subject to GSTIN documentation</x:v>
+      </x:c>
+      <x:c r="X2" s="16" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Y2" s="16" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Z2" s="16" t="str">
+        <x:v>N</x:v>
+      </x:c>
+      <x:c r="AA2" s="16" t="str"/>
+      <x:c r="AB2" s="16" t="str">
+        <x:v>CPC email dated 11-02-2026; rate stated as ₹750 for 70 QTY. Tax split not recovered.</x:v>
+      </x:c>
+      <x:c r="AC2" s="16" t="str">
+        <x:v>Y</x:v>
+      </x:c>
+      <x:c r="AD2" s="16" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="16" t="str">
+        <x:v>QUOTE-E0159A4AB620</x:v>
+      </x:c>
+      <x:c r="B3" s="16" t="str">
+        <x:v>PROC-HIST-MP-LKD-2026-08-LAPTOP</x:v>
+      </x:c>
+      <x:c r="C3" s="16" t="str">
+        <x:v>ITEM-A5500989C3EA</x:v>
+      </x:c>
+      <x:c r="D3" s="16" t="str">
+        <x:v>Laptop - 04</x:v>
+      </x:c>
+      <x:c r="E3" s="16" t="str">
+        <x:v>laptop computer</x:v>
+      </x:c>
+      <x:c r="F3" s="16" t="str">
+        <x:v>IT equipment</x:v>
+      </x:c>
+      <x:c r="G3" s="16" t="str">
+        <x:v>Intel Core i3; 8 GB RAM; 512 GB SSD; 15.6-inch display; bag; 1-year warranty. HP 15-FD0624TU quoted by two vendors; Dell DC15250 quoted by Computer Bazar.</x:v>
+      </x:c>
+      <x:c r="H3" s="16" t="str">
+        <x:v>LAPTOP-I3-8GB-512SSD-15.6IN-BAG-1YR-V1</x:v>
+      </x:c>
+      <x:c r="I3" s="16" t="str">
+        <x:v>4.0</x:v>
+      </x:c>
+      <x:c r="J3" s="16" t="str">
+        <x:v>unit</x:v>
+      </x:c>
+      <x:c r="K3" s="16" t="str">
+        <x:v>unit</x:v>
+      </x:c>
+      <x:c r="L3" s="16" t="str">
+        <x:v>VEND-4EC18E1C2633</x:v>
+      </x:c>
+      <x:c r="M3" s="16" t="str">
+        <x:v>M.P. Computer &amp; Electronics</x:v>
+      </x:c>
+      <x:c r="N3" s="16" t="str"/>
+      <x:c r="O3" s="16" t="str">
+        <x:v>56500</x:v>
+      </x:c>
+      <x:c r="P3" s="16" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q3" s="16" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R3" s="16" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S3" s="16" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T3" s="16" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U3" s="16" t="str">
+        <x:v>56500.0</x:v>
+      </x:c>
+      <x:c r="V3" s="16" t="str">
+        <x:v>226000.0</x:v>
+      </x:c>
+      <x:c r="W3" s="16" t="str">
+        <x:v>Responsive subject to authorization/selection clarification</x:v>
+      </x:c>
+      <x:c r="X3" s="16" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Y3" s="16" t="str"/>
+      <x:c r="Z3" s="16" t="str">
+        <x:v>N</x:v>
+      </x:c>
+      <x:c r="AA3" s="16" t="str"/>
+      <x:c r="AB3" s="16" t="str">
+        <x:v>Purchase Committee Note _Laptop.docx.pdf; HP 15-FD0624TU; quoted unit rate ₹56,500; GST stated included.</x:v>
+      </x:c>
+      <x:c r="AC3" s="16" t="str">
+        <x:v>Y</x:v>
+      </x:c>
+      <x:c r="AD3" s="16" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="16" t="str">
+        <x:v>QUOTE-4F0BD1922CB8</x:v>
+      </x:c>
+      <x:c r="B4" s="16" t="str">
+        <x:v>PROC-HIST-MP-LKD-2026-08-LAPTOP</x:v>
+      </x:c>
+      <x:c r="C4" s="16" t="str">
+        <x:v>ITEM-A5500989C3EA</x:v>
+      </x:c>
+      <x:c r="D4" s="16" t="str">
+        <x:v>Laptop - 04</x:v>
+      </x:c>
+      <x:c r="E4" s="16" t="str">
+        <x:v>laptop computer</x:v>
+      </x:c>
+      <x:c r="F4" s="16" t="str">
+        <x:v>IT equipment</x:v>
+      </x:c>
+      <x:c r="G4" s="16" t="str">
+        <x:v>Intel Core i3; 8 GB RAM; 512 GB SSD; 15.6-inch display; bag; 1-year warranty. HP 15-FD0624TU quoted by two vendors; Dell DC15250 quoted by Computer Bazar.</x:v>
+      </x:c>
+      <x:c r="H4" s="16" t="str">
+        <x:v>LAPTOP-I3-8GB-512SSD-15.6IN-BAG-1YR-V1</x:v>
+      </x:c>
+      <x:c r="I4" s="16" t="str">
+        <x:v>4.0</x:v>
+      </x:c>
+      <x:c r="J4" s="16" t="str">
+        <x:v>unit</x:v>
+      </x:c>
+      <x:c r="K4" s="16" t="str">
+        <x:v>unit</x:v>
+      </x:c>
+      <x:c r="L4" s="16" t="str">
+        <x:v>VEND-F817ECC50FDD</x:v>
+      </x:c>
+      <x:c r="M4" s="16" t="str">
+        <x:v>Computer Vision</x:v>
+      </x:c>
+      <x:c r="N4" s="16" t="str"/>
+      <x:c r="O4" s="16" t="str">
+        <x:v>56500</x:v>
+      </x:c>
+      <x:c r="P4" s="16" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q4" s="16" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R4" s="16" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S4" s="16" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T4" s="16" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U4" s="16" t="str">
+        <x:v>56500.0</x:v>
+      </x:c>
+      <x:c r="V4" s="16" t="str">
+        <x:v>226000.0</x:v>
+      </x:c>
+      <x:c r="W4" s="16" t="str">
+        <x:v>Responsive</x:v>
+      </x:c>
+      <x:c r="X4" s="16" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Y4" s="16" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Z4" s="16" t="str">
+        <x:v>N</x:v>
+      </x:c>
+      <x:c r="AA4" s="16" t="str"/>
+      <x:c r="AB4" s="16" t="str">
+        <x:v>Purchase Committee Note _Laptop.docx.pdf; HP 15-FD0624TU; quoted unit rate ₹56,500; GST stated included; selected due to company authorization.</x:v>
+      </x:c>
+      <x:c r="AC4" s="16" t="str">
+        <x:v>Y</x:v>
+      </x:c>
+      <x:c r="AD4" s="16" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="16" t="str">
+        <x:v>QUOTE-82C503169C10</x:v>
+      </x:c>
+      <x:c r="B5" s="16" t="str">
+        <x:v>PROC-HIST-MP-LKD-2026-08-LAPTOP</x:v>
+      </x:c>
+      <x:c r="C5" s="16" t="str">
+        <x:v>ITEM-A5500989C3EA</x:v>
+      </x:c>
+      <x:c r="D5" s="16" t="str">
+        <x:v>Laptop - 04</x:v>
+      </x:c>
+      <x:c r="E5" s="16" t="str">
+        <x:v>laptop computer</x:v>
+      </x:c>
+      <x:c r="F5" s="16" t="str">
+        <x:v>IT equipment</x:v>
+      </x:c>
+      <x:c r="G5" s="16" t="str">
+        <x:v>Intel Core i3; 8 GB RAM; 512 GB SSD; 15.6-inch display; bag; 1-year warranty. HP 15-FD0624TU quoted by two vendors; Dell DC15250 quoted by Computer Bazar.</x:v>
+      </x:c>
+      <x:c r="H5" s="16" t="str">
+        <x:v>LAPTOP-I3-8GB-512SSD-15.6IN-BAG-1YR-V1</x:v>
+      </x:c>
+      <x:c r="I5" s="16" t="str">
+        <x:v>4.0</x:v>
+      </x:c>
+      <x:c r="J5" s="16" t="str">
+        <x:v>unit</x:v>
+      </x:c>
+      <x:c r="K5" s="16" t="str">
+        <x:v>unit</x:v>
+      </x:c>
+      <x:c r="L5" s="16" t="str">
+        <x:v>VEND-A091EBFF28FC</x:v>
+      </x:c>
+      <x:c r="M5" s="16" t="str">
+        <x:v>Computer Bazar</x:v>
+      </x:c>
+      <x:c r="N5" s="16" t="str"/>
+      <x:c r="O5" s="16" t="str">
+        <x:v>59500</x:v>
+      </x:c>
+      <x:c r="P5" s="16" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q5" s="16" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R5" s="16" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S5" s="16" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T5" s="16" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U5" s="16" t="str">
+        <x:v>59500.0</x:v>
+      </x:c>
+      <x:c r="V5" s="16" t="str">
+        <x:v>238000.0</x:v>
+      </x:c>
+      <x:c r="W5" s="16" t="str">
+        <x:v>Responsive</x:v>
+      </x:c>
+      <x:c r="X5" s="16" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Y5" s="16" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="Z5" s="16" t="str">
+        <x:v>N</x:v>
+      </x:c>
+      <x:c r="AA5" s="16" t="str"/>
+      <x:c r="AB5" s="16" t="str">
+        <x:v>Purchase Committee Note _Laptop.docx.pdf; Dell DC15250; quoted unit rate ₹59,500; GST stated included.</x:v>
+      </x:c>
+      <x:c r="AC5" s="16" t="str">
+        <x:v>Y</x:v>
+      </x:c>
+      <x:c r="AD5" s="16" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -957,120 +1248,120 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="23" t="str">
+      <x:c r="A1" s="21" t="str">
         <x:v>award_id</x:v>
       </x:c>
-      <x:c r="B1" s="23" t="str">
+      <x:c r="B1" s="21" t="str">
         <x:v>procurement_id</x:v>
       </x:c>
-      <x:c r="C1" s="23" t="str">
+      <x:c r="C1" s="21" t="str">
         <x:v>procurement_date</x:v>
       </x:c>
-      <x:c r="D1" s="23" t="str">
+      <x:c r="D1" s="21" t="str">
         <x:v>financial_year</x:v>
       </x:c>
-      <x:c r="E1" s="23" t="str">
+      <x:c r="E1" s="21" t="str">
         <x:v>quarter</x:v>
       </x:c>
-      <x:c r="F1" s="23" t="str">
+      <x:c r="F1" s="21" t="str">
         <x:v>state</x:v>
       </x:c>
-      <x:c r="G1" s="23" t="str">
+      <x:c r="G1" s="21" t="str">
         <x:v>project_unit</x:v>
       </x:c>
-      <x:c r="H1" s="23" t="str">
+      <x:c r="H1" s="21" t="str">
         <x:v>funding_partner</x:v>
       </x:c>
-      <x:c r="I1" s="23" t="str">
+      <x:c r="I1" s="21" t="str">
         <x:v>procurement_reference</x:v>
       </x:c>
-      <x:c r="J1" s="23" t="str">
+      <x:c r="J1" s="21" t="str">
         <x:v>item_id</x:v>
       </x:c>
-      <x:c r="K1" s="23" t="str">
+      <x:c r="K1" s="21" t="str">
         <x:v>normalized_item_name</x:v>
       </x:c>
-      <x:c r="L1" s="23" t="str">
+      <x:c r="L1" s="21" t="str">
         <x:v>item_category</x:v>
       </x:c>
-      <x:c r="M1" s="23" t="str">
+      <x:c r="M1" s="21" t="str">
         <x:v>specification_key</x:v>
       </x:c>
-      <x:c r="N1" s="23" t="str">
+      <x:c r="N1" s="21" t="str">
         <x:v>canonical_unit</x:v>
       </x:c>
-      <x:c r="O1" s="23" t="str">
+      <x:c r="O1" s="21" t="str">
         <x:v>awarded_quantity</x:v>
       </x:c>
-      <x:c r="P1" s="23" t="str">
+      <x:c r="P1" s="21" t="str">
         <x:v>vendor_id</x:v>
       </x:c>
-      <x:c r="Q1" s="23" t="str">
+      <x:c r="Q1" s="21" t="str">
         <x:v>vendor_name</x:v>
       </x:c>
-      <x:c r="R1" s="23" t="str">
+      <x:c r="R1" s="21" t="str">
         <x:v>awarded_base_unit_rate</x:v>
       </x:c>
-      <x:c r="S1" s="23" t="str">
+      <x:c r="S1" s="21" t="str">
         <x:v>gst_percent</x:v>
       </x:c>
-      <x:c r="T1" s="23" t="str">
+      <x:c r="T1" s="21" t="str">
         <x:v>freight_per_unit</x:v>
       </x:c>
-      <x:c r="U1" s="23" t="str">
+      <x:c r="U1" s="21" t="str">
         <x:v>installation_per_unit</x:v>
       </x:c>
-      <x:c r="V1" s="23" t="str">
+      <x:c r="V1" s="21" t="str">
         <x:v>other_per_unit</x:v>
       </x:c>
-      <x:c r="W1" s="23" t="str">
+      <x:c r="W1" s="21" t="str">
         <x:v>awarded_landed_unit_rate</x:v>
       </x:c>
-      <x:c r="X1" s="23" t="str">
+      <x:c r="X1" s="21" t="str">
         <x:v>award_total</x:v>
       </x:c>
-      <x:c r="Y1" s="23" t="str">
+      <x:c r="Y1" s="21" t="str">
         <x:v>currency</x:v>
       </x:c>
-      <x:c r="Z1" s="23" t="str">
+      <x:c r="Z1" s="21" t="str">
         <x:v>cpc_verdict</x:v>
       </x:c>
-      <x:c r="AA1" s="23" t="str">
+      <x:c r="AA1" s="21" t="str">
         <x:v>benchmark_eligible</x:v>
       </x:c>
-      <x:c r="AB1" s="23" t="str">
+      <x:c r="AB1" s="21" t="str">
         <x:v>source_reference</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="17"/>
-      <x:c r="B2" s="17"/>
-      <x:c r="C2" s="17"/>
-      <x:c r="D2" s="17"/>
-      <x:c r="E2" s="17"/>
-      <x:c r="F2" s="17"/>
-      <x:c r="G2" s="17"/>
-      <x:c r="H2" s="17"/>
-      <x:c r="I2" s="17"/>
-      <x:c r="J2" s="17"/>
-      <x:c r="K2" s="17"/>
-      <x:c r="L2" s="17"/>
-      <x:c r="M2" s="17"/>
-      <x:c r="N2" s="17"/>
-      <x:c r="O2" s="17"/>
-      <x:c r="P2" s="17"/>
-      <x:c r="Q2" s="17"/>
-      <x:c r="R2" s="17"/>
-      <x:c r="S2" s="17"/>
-      <x:c r="T2" s="17"/>
-      <x:c r="U2" s="17"/>
-      <x:c r="V2" s="17"/>
-      <x:c r="W2" s="17"/>
-      <x:c r="X2" s="17"/>
-      <x:c r="Y2" s="17"/>
-      <x:c r="Z2" s="17"/>
-      <x:c r="AA2" s="17"/>
-      <x:c r="AB2" s="17"/>
+      <x:c r="A2" s="16"/>
+      <x:c r="B2" s="16"/>
+      <x:c r="C2" s="16"/>
+      <x:c r="D2" s="16"/>
+      <x:c r="E2" s="16"/>
+      <x:c r="F2" s="16"/>
+      <x:c r="G2" s="16"/>
+      <x:c r="H2" s="16"/>
+      <x:c r="I2" s="16"/>
+      <x:c r="J2" s="16"/>
+      <x:c r="K2" s="16"/>
+      <x:c r="L2" s="16"/>
+      <x:c r="M2" s="16"/>
+      <x:c r="N2" s="16"/>
+      <x:c r="O2" s="16"/>
+      <x:c r="P2" s="16"/>
+      <x:c r="Q2" s="16"/>
+      <x:c r="R2" s="16"/>
+      <x:c r="S2" s="16"/>
+      <x:c r="T2" s="16"/>
+      <x:c r="U2" s="16"/>
+      <x:c r="V2" s="16"/>
+      <x:c r="W2" s="16"/>
+      <x:c r="X2" s="16"/>
+      <x:c r="Y2" s="16"/>
+      <x:c r="Z2" s="16"/>
+      <x:c r="AA2" s="16"/>
+      <x:c r="AB2" s="16"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1081,56 +1372,153 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="6.380000114440918" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="18.6299991607666" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="11.5" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="16.5" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="19.5" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="19.8799991607666" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="11.75" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="13.630000114440918" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="17.75" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="33.130001068115234" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="183" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="5.130000114440918" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="4.75" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="10.5" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="23" t="str">
+      <x:c r="A1" s="21" t="str">
         <x:v>item_id</x:v>
       </x:c>
-      <x:c r="B1" s="23" t="str">
+      <x:c r="B1" s="21" t="str">
         <x:v>normalized_item_name</x:v>
       </x:c>
-      <x:c r="C1" s="23" t="str">
+      <x:c r="C1" s="21" t="str">
         <x:v>item_category</x:v>
       </x:c>
-      <x:c r="D1" s="23" t="str">
+      <x:c r="D1" s="21" t="str">
         <x:v>canonical_unit</x:v>
       </x:c>
-      <x:c r="E1" s="23" t="str">
+      <x:c r="E1" s="21" t="str">
         <x:v>specification_key</x:v>
       </x:c>
-      <x:c r="F1" s="23" t="str">
+      <x:c r="F1" s="21" t="str">
         <x:v>standard_specification</x:v>
       </x:c>
-      <x:c r="G1" s="23" t="str">
+      <x:c r="G1" s="21" t="str">
         <x:v>active</x:v>
       </x:c>
-      <x:c r="H1" s="23" t="str">
+      <x:c r="H1" s="21" t="str">
         <x:v>notes</x:v>
       </x:c>
-      <x:c r="I1" s="23" t="str">
+      <x:c r="I1" s="21" t="str">
         <x:v>last_updated</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="17"/>
-      <x:c r="B2" s="17"/>
-      <x:c r="C2" s="17"/>
-      <x:c r="D2" s="17"/>
-      <x:c r="E2" s="17"/>
-      <x:c r="F2" s="17"/>
-      <x:c r="G2" s="17"/>
-      <x:c r="H2" s="17"/>
-      <x:c r="I2" s="17"/>
+      <x:c r="A2" s="16" t="str">
+        <x:v>ITEM-BDBB344470B0</x:v>
+      </x:c>
+      <x:c r="B2" s="16" t="str">
+        <x:v>office water bottle</x:v>
+      </x:c>
+      <x:c r="C2" s="16" t="str">
+        <x:v>Staff kit</x:v>
+      </x:c>
+      <x:c r="D2" s="16" t="str">
+        <x:v>unit</x:v>
+      </x:c>
+      <x:c r="E2" s="16" t="str">
+        <x:v>UNSPECIFIED</x:v>
+      </x:c>
+      <x:c r="F2" s="16" t="str">
+        <x:v>Detailed bottle specification not recovered. CPC email records L1 vendor Mehul Vasan Bhandar at a rate of ₹750 for 70 quantity; GST was stated as included but GSTIN was initially missing.</x:v>
+      </x:c>
+      <x:c r="G2" s="16" t="str">
+        <x:v>Y</x:v>
+      </x:c>
+      <x:c r="H2" s="16" t="str"/>
+      <x:c r="I2" s="16" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="16" t="str">
+        <x:v>ITEM-8A23D2907380</x:v>
+      </x:c>
+      <x:c r="B3" s="16" t="str">
+        <x:v>office staff bag</x:v>
+      </x:c>
+      <x:c r="C3" s="16" t="str">
+        <x:v>Staff kit</x:v>
+      </x:c>
+      <x:c r="D3" s="16" t="str">
+        <x:v>unit</x:v>
+      </x:c>
+      <x:c r="E3" s="16" t="str">
+        <x:v>UNSPECIFIED</x:v>
+      </x:c>
+      <x:c r="F3" s="16" t="str">
+        <x:v>Detailed bag specification, quantity and rate not recovered from saved evidence. ASE Enterprise is identified as the L1 vendor; CPC required sample/quality verification and comparison with previous Mehsana-Visnagar purchase before proceeding.</x:v>
+      </x:c>
+      <x:c r="G3" s="16" t="str">
+        <x:v>Y</x:v>
+      </x:c>
+      <x:c r="H3" s="16" t="str"/>
+      <x:c r="I3" s="16" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="16" t="str">
+        <x:v>ITEM-A5500989C3EA</x:v>
+      </x:c>
+      <x:c r="B4" s="16" t="str">
+        <x:v>laptop computer</x:v>
+      </x:c>
+      <x:c r="C4" s="16" t="str">
+        <x:v>IT equipment</x:v>
+      </x:c>
+      <x:c r="D4" s="16" t="str">
+        <x:v>unit</x:v>
+      </x:c>
+      <x:c r="E4" s="16" t="str">
+        <x:v>LAPTOP-I3-8GB-512SSD-15.6IN-BAG-1YR-V1</x:v>
+      </x:c>
+      <x:c r="F4" s="16" t="str">
+        <x:v>Intel Core i3; 8 GB RAM; 512 GB SSD; 15.6-inch display; bag; 1-year warranty. HP 15-FD0624TU quoted by two vendors; Dell DC15250 quoted by Computer Bazar.</x:v>
+      </x:c>
+      <x:c r="G4" s="16" t="str">
+        <x:v>Y</x:v>
+      </x:c>
+      <x:c r="H4" s="16" t="str"/>
+      <x:c r="I4" s="16" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="16" t="str">
+        <x:v>ITEM-EA4941B4391B</x:v>
+      </x:c>
+      <x:c r="B5" s="16" t="str">
+        <x:v>grass seeding biodiversity</x:v>
+      </x:c>
+      <x:c r="C5" s="16" t="str">
+        <x:v>Biodiversity / field activity</x:v>
+      </x:c>
+      <x:c r="D5" s="16" t="str">
+        <x:v>UNSPECIFIED</x:v>
+      </x:c>
+      <x:c r="E5" s="16" t="str">
+        <x:v>UNSPECIFIED</x:v>
+      </x:c>
+      <x:c r="F5" s="16" t="str">
+        <x:v>Scope, unit, quantity, vendor names and rates not recovered from saved evidence.</x:v>
+      </x:c>
+      <x:c r="G5" s="16" t="str">
+        <x:v>Y</x:v>
+      </x:c>
+      <x:c r="H5" s="16" t="str"/>
+      <x:c r="I5" s="16" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1141,56 +1529,168 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="8.25" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="11.130000114440918" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="16.8799991607666" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="21.75" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="20.6299991607666" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="11" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="11.5" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="13" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="15.880000114440918" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="10.75" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="5.130000114440918" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="4.75" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="92.12999725341797" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="10.5" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="23" t="str">
+      <x:c r="A1" s="21" t="str">
         <x:v>vendor_id</x:v>
       </x:c>
-      <x:c r="B1" s="23" t="str">
+      <x:c r="B1" s="21" t="str">
         <x:v>vendor_name</x:v>
       </x:c>
-      <x:c r="C1" s="23" t="str">
+      <x:c r="C1" s="21" t="str">
         <x:v>vendor_name_normalized</x:v>
       </x:c>
-      <x:c r="D1" s="23" t="str">
+      <x:c r="D1" s="21" t="str">
         <x:v>states_served</x:v>
       </x:c>
-      <x:c r="E1" s="23" t="str">
+      <x:c r="E1" s="21" t="str">
         <x:v>gstin_optional</x:v>
       </x:c>
-      <x:c r="F1" s="23" t="str">
+      <x:c r="F1" s="21" t="str">
         <x:v>pan_optional</x:v>
       </x:c>
-      <x:c r="G1" s="23" t="str">
+      <x:c r="G1" s="21" t="str">
         <x:v>active</x:v>
       </x:c>
-      <x:c r="H1" s="23" t="str">
+      <x:c r="H1" s="21" t="str">
         <x:v>notes</x:v>
       </x:c>
-      <x:c r="I1" s="23" t="str">
+      <x:c r="I1" s="21" t="str">
         <x:v>last_updated</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="17"/>
-      <x:c r="B2" s="17"/>
-      <x:c r="C2" s="17"/>
-      <x:c r="D2" s="17"/>
-      <x:c r="E2" s="17"/>
-      <x:c r="F2" s="17"/>
-      <x:c r="G2" s="17"/>
-      <x:c r="H2" s="17"/>
-      <x:c r="I2" s="17"/>
+      <x:c r="A2" s="16" t="str">
+        <x:v>VEND-59C44BBC65A6</x:v>
+      </x:c>
+      <x:c r="B2" s="16" t="str">
+        <x:v>Mehul Vasan Bhandar</x:v>
+      </x:c>
+      <x:c r="C2" s="16" t="str">
+        <x:v>mehul vasan bhandar</x:v>
+      </x:c>
+      <x:c r="D2" s="16" t="str">
+        <x:v>Gujarat</x:v>
+      </x:c>
+      <x:c r="E2" s="16" t="str"/>
+      <x:c r="F2" s="16" t="str"/>
+      <x:c r="G2" s="16" t="str">
+        <x:v>Y</x:v>
+      </x:c>
+      <x:c r="H2" s="16" t="str"/>
+      <x:c r="I2" s="16" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="16" t="str">
+        <x:v>VEND-4EC18E1C2633</x:v>
+      </x:c>
+      <x:c r="B3" s="16" t="str">
+        <x:v>M.P. Computer &amp; Electronics</x:v>
+      </x:c>
+      <x:c r="C3" s="16" t="str">
+        <x:v>m p computer electronics</x:v>
+      </x:c>
+      <x:c r="D3" s="16" t="str">
+        <x:v>Madhya Pradesh</x:v>
+      </x:c>
+      <x:c r="E3" s="16" t="str">
+        <x:v>23AQNPS2772A1ZW</x:v>
+      </x:c>
+      <x:c r="F3" s="16" t="str"/>
+      <x:c r="G3" s="16" t="str">
+        <x:v>Y</x:v>
+      </x:c>
+      <x:c r="H3" s="16" t="str"/>
+      <x:c r="I3" s="16" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="16" t="str">
+        <x:v>VEND-F817ECC50FDD</x:v>
+      </x:c>
+      <x:c r="B4" s="16" t="str">
+        <x:v>Computer Vision</x:v>
+      </x:c>
+      <x:c r="C4" s="16" t="str">
+        <x:v>computer vision</x:v>
+      </x:c>
+      <x:c r="D4" s="16" t="str">
+        <x:v>Madhya Pradesh</x:v>
+      </x:c>
+      <x:c r="E4" s="16" t="str">
+        <x:v>23AFHPC5017R1ZE</x:v>
+      </x:c>
+      <x:c r="F4" s="16" t="str"/>
+      <x:c r="G4" s="16" t="str">
+        <x:v>Y</x:v>
+      </x:c>
+      <x:c r="H4" s="16" t="str"/>
+      <x:c r="I4" s="16" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="16" t="str">
+        <x:v>VEND-A091EBFF28FC</x:v>
+      </x:c>
+      <x:c r="B5" s="16" t="str">
+        <x:v>Computer Bazar</x:v>
+      </x:c>
+      <x:c r="C5" s="16" t="str">
+        <x:v>computer bazar</x:v>
+      </x:c>
+      <x:c r="D5" s="16" t="str">
+        <x:v>Madhya Pradesh</x:v>
+      </x:c>
+      <x:c r="E5" s="16" t="str">
+        <x:v>23ACGPJ7286B1ZS</x:v>
+      </x:c>
+      <x:c r="F5" s="16" t="str"/>
+      <x:c r="G5" s="16" t="str">
+        <x:v>Y</x:v>
+      </x:c>
+      <x:c r="H5" s="16" t="str"/>
+      <x:c r="I5" s="16" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="16" t="str">
+        <x:v>VEND-E378C6296DD7</x:v>
+      </x:c>
+      <x:c r="B6" s="16" t="str">
+        <x:v>ASE Enterprise</x:v>
+      </x:c>
+      <x:c r="C6" s="16" t="str">
+        <x:v>ase enterprise</x:v>
+      </x:c>
+      <x:c r="D6" s="16" t="str">
+        <x:v>Gujarat</x:v>
+      </x:c>
+      <x:c r="E6" s="16" t="str"/>
+      <x:c r="F6" s="16" t="str"/>
+      <x:c r="G6" s="16" t="str">
+        <x:v>Y</x:v>
+      </x:c>
+      <x:c r="H6" s="16" t="str">
+        <x:v>Historical proposed L1 for office staff bag; quantity/rate not recoverable from saved CPC evidence; not a benchmark record.</x:v>
+      </x:c>
+      <x:c r="I6" s="16" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1209,28 +1709,28 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="23" t="str">
+      <x:c r="A1" s="21" t="str">
         <x:v>alias</x:v>
       </x:c>
-      <x:c r="B1" s="23" t="str">
+      <x:c r="B1" s="21" t="str">
         <x:v>normalized_item_name</x:v>
       </x:c>
-      <x:c r="C1" s="23" t="str">
+      <x:c r="C1" s="21" t="str">
         <x:v>item_category</x:v>
       </x:c>
-      <x:c r="D1" s="23" t="str">
+      <x:c r="D1" s="21" t="str">
         <x:v>canonical_unit</x:v>
       </x:c>
-      <x:c r="E1" s="23" t="str">
+      <x:c r="E1" s="21" t="str">
         <x:v>notes</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="17"/>
-      <x:c r="B2" s="17"/>
-      <x:c r="C2" s="17"/>
-      <x:c r="D2" s="17"/>
-      <x:c r="E2" s="17"/>
+      <x:c r="A2" s="16"/>
+      <x:c r="B2" s="16"/>
+      <x:c r="C2" s="16"/>
+      <x:c r="D2" s="16"/>
+      <x:c r="E2" s="16"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
